--- a/BoM/Costs/nixie-bom.xlsx
+++ b/BoM/Costs/nixie-bom.xlsx
@@ -743,7 +743,7 @@
     <t>Created:</t>
   </si>
   <si>
-    <t>2024-10-05 23:26:22</t>
+    <t>2024-10-06 08:36:17</t>
   </si>
   <si>
     <t>KiCost® v1.1.19 + KiBot v1.8.1</t>
